--- a/src/main/resources/input/KING/props/KING.xlsx
+++ b/src/main/resources/input/KING/props/KING.xlsx
@@ -3,30 +3,40 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\github.com\Imvertor-Maven\src\main\resources\input\KING\props\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C26B49E-64D6-4FAF-8B42-D6755A1C9399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{E4A698A4-7767-4469-8E6D-EE0B5D05ACC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5610" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-7960" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KING" sheetId="3" r:id="rId1"/>
     <sheet name="Explanation" sheetId="4" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="442">
   <si>
     <t>Name</t>
   </si>
@@ -169,6 +179,15 @@
     <t>Yes if the released application should be zipped for distribution</t>
   </si>
   <si>
+    <t>dashboardpath</t>
+  </si>
+  <si>
+    <t>http-path</t>
+  </si>
+  <si>
+    <t>The path to the Imvertor dashboard application.</t>
+  </si>
+  <si>
     <t>debug</t>
   </si>
   <si>
@@ -896,6 +915,9 @@
   </si>
   <si>
     <t>msword</t>
+  </si>
+  <si>
+    <t>https://imvertor.armatiek.nl/imvertor-executor/dashboard</t>
   </si>
   <si>
     <t>string</t>
@@ -1210,6 +1232,11 @@
     <t>niet voor VNG geloof ik</t>
   </si>
   <si>
+    <t>Voor Kennisnet staat deze geïndiceerd als niet relevant voor hen. Waarom?
+Je mag deze waarde helemaal niet specificeren als gebruiker. Toch gebeurt dat in de minimale configuratie.
+Handiger om leeg te laten</t>
+  </si>
+  <si>
     <t>Waarom heeft static een waarde als het niet wordt gebruikt door Kennisnet?
 Je mag deze waarde helemaal niet specificeren als gebruiker. Toch gebeurt dat in de minimale configuratie.
 Weglaten</t>
@@ -1361,7 +1388,7 @@
     <t>officeexpansion</t>
   </si>
   <si>
-    <t>Yes if inherited attributes and relations are to be grouped by supertype and  indicated as inherited in Respec documentation.</t>
+    <t>Yes if inherited attributes and relations are grouped by supertype and indicated as inherited in Respec documentation.</t>
   </si>
 </sst>
 </file>
@@ -1963,7 +1990,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z159"/>
+  <dimension ref="A1:Z160"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.81640625" customWidth="1"/>
@@ -2003,126 +2030,126 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G1" s="10"/>
       <c r="H1" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="M1" s="10"/>
       <c r="N1" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="S1" s="10"/>
       <c r="T1" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2" spans="1:26" s="3" customFormat="1" ht="56.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="F2" s="31"/>
       <c r="G2" s="11"/>
       <c r="H2" s="2" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="M2" s="11"/>
       <c r="N2" s="2" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="S2" s="11"/>
       <c r="T2" s="2" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="3" spans="1:26" s="1" customFormat="1" ht="44" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D3" s="4" t="b">
         <v>0</v>
@@ -2183,13 +2210,13 @@
     </row>
     <row r="6" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D6" s="4" t="b">
         <v>0</v>
@@ -2223,10 +2250,10 @@
       <c r="M7" s="12"/>
       <c r="S7" s="12"/>
       <c r="Y7" s="42" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="8" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
@@ -2242,13 +2269,13 @@
     </row>
     <row r="9" spans="1:26" s="4" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D9" s="4" t="b">
         <v>0</v>
@@ -2263,10 +2290,10 @@
       <c r="M9" s="12"/>
       <c r="S9" s="12"/>
       <c r="Y9" s="21" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Z9" s="4" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
@@ -2294,13 +2321,13 @@
     </row>
     <row r="11" spans="1:26" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D11" s="4" t="b">
         <v>0</v>
@@ -2315,13 +2342,13 @@
     </row>
     <row r="12" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D12" s="4" t="b">
         <v>0</v>
@@ -2336,13 +2363,13 @@
     </row>
     <row r="13" spans="1:26" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D13" s="4" t="b">
         <v>0</v>
@@ -2355,10 +2382,10 @@
       <c r="M13" s="12"/>
       <c r="S13" s="12"/>
       <c r="Y13" s="22" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="14" spans="1:26" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -2407,10 +2434,10 @@
       <c r="M15" s="12"/>
       <c r="S15" s="12"/>
       <c r="Y15" s="22" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="16" spans="1:26" s="1" customFormat="1" ht="87" x14ac:dyDescent="0.35">
@@ -2430,24 +2457,24 @@
         <v>0</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="G16" s="12"/>
       <c r="M16" s="12"/>
       <c r="S16" s="12"/>
       <c r="Y16" s="22" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="17" spans="1:26" s="1" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D17" s="1" t="b">
         <v>1</v>
@@ -2456,7 +2483,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G17" s="12"/>
       <c r="M17" s="12"/>
@@ -2464,13 +2491,13 @@
     </row>
     <row r="18" spans="1:26" s="1" customFormat="1" ht="156.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B18" s="32" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="D18" s="1" t="b">
         <v>1</v>
@@ -2479,72 +2506,72 @@
         <v>1</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="G18" s="12"/>
       <c r="H18" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="M18" s="12"/>
       <c r="N18" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="S18" s="12"/>
       <c r="T18" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="V18" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="X18" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="Y18" s="22" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="19" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D19" s="1" t="b">
         <v>0</v>
@@ -2553,7 +2580,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G19" s="12"/>
       <c r="M19" s="12"/>
@@ -2561,13 +2588,13 @@
     </row>
     <row r="20" spans="1:26" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D20" s="1" t="b">
         <v>0</v>
@@ -2576,24 +2603,24 @@
         <v>1</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="G20" s="12"/>
       <c r="M20" s="12"/>
       <c r="S20" s="12"/>
       <c r="Y20" s="22" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="21" spans="1:26" s="1" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D21" s="1" t="b">
         <v>0</v>
@@ -2602,24 +2629,24 @@
         <v>1</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="G21" s="12"/>
       <c r="M21" s="12"/>
       <c r="S21" s="12"/>
       <c r="Y21" s="22" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="22" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D22" s="1" t="b">
         <v>0</v>
@@ -2634,10 +2661,10 @@
       <c r="M22" s="12"/>
       <c r="S22" s="12"/>
       <c r="Y22" s="22" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="23" spans="1:26" s="4" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
@@ -2667,21 +2694,21 @@
       <c r="R23" s="1"/>
       <c r="S23" s="12"/>
       <c r="Y23" s="21" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="Z23" s="4" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="24" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D24" s="4" t="b">
         <v>0</v>
@@ -2717,10 +2744,10 @@
       <c r="M25" s="12"/>
       <c r="S25" s="12"/>
       <c r="Y25" s="22" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="26" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
@@ -2764,12 +2791,12 @@
         <v>4</v>
       </c>
       <c r="Y26" s="22" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="27" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>5</v>
@@ -2808,7 +2835,7 @@
         <v>4</v>
       </c>
       <c r="Y27" s="22" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="28" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
@@ -2834,18 +2861,18 @@
       <c r="M28" s="12"/>
       <c r="S28" s="12"/>
       <c r="Y28" s="22" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="29" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D29" s="1" t="b">
         <v>0</v>
@@ -2860,18 +2887,18 @@
       <c r="M29" s="12"/>
       <c r="S29" s="12"/>
       <c r="Y29" s="22" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="30" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D30" s="4" t="b">
         <v>0</v>
@@ -2884,18 +2911,18 @@
       <c r="M30" s="12"/>
       <c r="S30" s="12"/>
       <c r="Y30" s="22" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="31" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D31" s="4" t="b">
         <v>0</v>
@@ -2908,18 +2935,18 @@
       <c r="M31" s="12"/>
       <c r="S31" s="12"/>
       <c r="Y31" s="22" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="32" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D32" s="4" t="b">
         <v>0</v>
@@ -2928,7 +2955,7 @@
         <v>1</v>
       </c>
       <c r="F32" s="27" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="G32" s="12"/>
       <c r="M32" s="12"/>
@@ -2936,7 +2963,7 @@
       <c r="U32" s="19"/>
       <c r="X32" s="19"/>
       <c r="Y32" s="22" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="33" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
@@ -2974,18 +3001,18 @@
       <c r="M33" s="12"/>
       <c r="S33" s="12"/>
       <c r="Y33" s="22" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="34" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D34" s="1" t="b">
         <v>0</v>
@@ -3000,18 +3027,18 @@
       <c r="M34" s="12"/>
       <c r="S34" s="12"/>
       <c r="Y34" s="22" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="35" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D35" s="1" t="b">
         <v>0</v>
@@ -3020,7 +3047,7 @@
         <v>1</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G35" s="12"/>
       <c r="M35" s="12"/>
@@ -3029,13 +3056,13 @@
     </row>
     <row r="36" spans="1:26" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D36" s="1" t="b">
         <v>0</v>
@@ -3044,13 +3071,13 @@
         <v>1</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="G36" s="12"/>
       <c r="M36" s="12"/>
       <c r="S36" s="12"/>
       <c r="Y36" s="22" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="37" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
@@ -3076,13 +3103,13 @@
     </row>
     <row r="38" spans="1:26" s="17" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D38" s="4" t="b">
         <v>0</v>
@@ -3096,7 +3123,7 @@
       <c r="M38" s="18"/>
       <c r="S38" s="12"/>
       <c r="Y38" s="21" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="Z38" s="1"/>
     </row>
@@ -3146,10 +3173,10 @@
       <c r="M40" s="12"/>
       <c r="S40" s="12"/>
       <c r="Y40" s="22" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="Z40" s="1" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="41" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
@@ -3177,13 +3204,13 @@
     </row>
     <row r="42" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D42" s="4" t="b">
         <v>0</v>
@@ -3192,7 +3219,7 @@
         <v>1</v>
       </c>
       <c r="F42" s="27" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G42" s="12"/>
       <c r="M42" s="33"/>
@@ -3200,13 +3227,13 @@
     </row>
     <row r="43" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D43" s="1" t="b">
         <v>0</v>
@@ -3233,7 +3260,7 @@
         <v>4</v>
       </c>
       <c r="Y43" s="22" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="44" spans="1:26" s="4" customFormat="1" ht="87" x14ac:dyDescent="0.35">
@@ -3270,181 +3297,189 @@
       <c r="W44" s="17"/>
       <c r="X44" s="17"/>
       <c r="Y44" s="21" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="45" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="43" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26" s="4" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="43" t="s">
+      <c r="B45" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="C45" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D45" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="F45" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="G45" s="12"/>
+      <c r="H45" s="16"/>
+      <c r="M45" s="12"/>
+      <c r="N45" s="16"/>
+      <c r="O45" s="16"/>
+      <c r="P45" s="16"/>
+      <c r="Q45" s="16"/>
+      <c r="R45" s="16"/>
+      <c r="S45" s="12"/>
+      <c r="U45" s="16"/>
+      <c r="X45" s="16"/>
+      <c r="Y45" s="21" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="46" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="B46" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="C45" s="43" t="s">
-        <v>48</v>
-      </c>
-      <c r="D45" s="43" t="b">
-        <v>0</v>
-      </c>
-      <c r="E45" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F45" s="26" t="s">
+      <c r="C46" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="D46" s="43" t="b">
+        <v>0</v>
+      </c>
+      <c r="E46" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F46" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="G45" s="12"/>
-      <c r="M45" s="12"/>
-      <c r="S45" s="12"/>
-      <c r="Y45" s="42" t="s">
-        <v>347</v>
-      </c>
-      <c r="Z45" s="1" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="46" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="43"/>
-      <c r="B46" s="43"/>
-      <c r="C46" s="43"/>
-      <c r="D46" s="43"/>
-      <c r="F46" s="26"/>
       <c r="G46" s="12"/>
       <c r="M46" s="12"/>
       <c r="S46" s="12"/>
-      <c r="Y46" s="42"/>
-    </row>
-    <row r="47" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A47" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="D47" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E47" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="Y46" s="42" t="s">
+        <v>351</v>
+      </c>
+      <c r="Z46" s="1" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="43"/>
+      <c r="B47" s="43"/>
+      <c r="C47" s="43"/>
+      <c r="D47" s="43"/>
       <c r="F47" s="26"/>
       <c r="G47" s="12"/>
       <c r="M47" s="12"/>
       <c r="S47" s="12"/>
-    </row>
-    <row r="48" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="Y47" s="42"/>
+    </row>
+    <row r="48" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>49</v>
+        <v>175</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>5</v>
+        <v>176</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>50</v>
+        <v>177</v>
       </c>
       <c r="D48" s="1" t="b">
         <v>0</v>
       </c>
       <c r="E48" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F48" s="26" t="s">
-        <v>16</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F48" s="26"/>
       <c r="G48" s="12"/>
       <c r="M48" s="12"/>
       <c r="S48" s="12"/>
     </row>
-    <row r="49" spans="1:26" s="1" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B49" s="4" t="s">
+    <row r="49" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="B49" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D49" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E49" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F49" s="39" t="s">
-        <v>200</v>
-      </c>
-      <c r="G49" s="40"/>
-      <c r="M49" s="13"/>
+      <c r="D49" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="E49" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F49" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G49" s="12"/>
+      <c r="M49" s="12"/>
       <c r="S49" s="12"/>
-      <c r="Y49" s="22" t="s">
-        <v>329</v>
-      </c>
-      <c r="Z49" s="1" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="50" spans="1:26" s="1" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A50" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="B50" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="C50" s="32" t="s">
-        <v>398</v>
-      </c>
-      <c r="D50" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E50" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F50" s="26" t="s">
-        <v>399</v>
-      </c>
-      <c r="G50" s="13"/>
-      <c r="M50" s="12"/>
+    </row>
+    <row r="50" spans="1:26" s="1" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A50" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D50" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E50" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="G50" s="40"/>
+      <c r="M50" s="13"/>
       <c r="S50" s="12"/>
       <c r="Y50" s="22" t="s">
-        <v>353</v>
-      </c>
-      <c r="Z50"/>
-    </row>
-    <row r="51" spans="1:26" s="4" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="B51" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C51" s="17" t="s">
-        <v>176</v>
-      </c>
-      <c r="D51" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="E51" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F51" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="G51" s="12"/>
+        <v>333</v>
+      </c>
+      <c r="Z50" s="1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="51" spans="1:26" s="1" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A51" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B51" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="32" t="s">
+        <v>403</v>
+      </c>
+      <c r="D51" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F51" s="26" t="s">
+        <v>404</v>
+      </c>
+      <c r="G51" s="13"/>
       <c r="M51" s="12"/>
       <c r="S51" s="12"/>
-      <c r="Y51" s="21" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="52" spans="1:26" s="4" customFormat="1" ht="86.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Y51" s="22" t="s">
+        <v>357</v>
+      </c>
+      <c r="Z51"/>
+    </row>
+    <row r="52" spans="1:26" s="4" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>178</v>
+        <v>5</v>
       </c>
       <c r="C52" s="17" t="s">
         <v>179</v>
@@ -3455,60 +3490,64 @@
       <c r="E52" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="F52" s="28"/>
+      <c r="F52" s="28" t="s">
+        <v>4</v>
+      </c>
       <c r="G52" s="12"/>
       <c r="M52" s="12"/>
       <c r="S52" s="12"/>
-      <c r="U52" t="s">
-        <v>357</v>
-      </c>
-      <c r="V52" t="s">
-        <v>357</v>
-      </c>
-      <c r="W52" t="s">
-        <v>357</v>
-      </c>
-      <c r="X52" t="s">
-        <v>357</v>
-      </c>
       <c r="Y52" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="Z52" s="4" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="53" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D53" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E53" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F53" s="27"/>
-      <c r="G53" s="36"/>
+        <v>334</v>
+      </c>
+    </row>
+    <row r="53" spans="1:26" s="4" customFormat="1" ht="86.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="B53" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="C53" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="D53" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E53" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F53" s="28"/>
+      <c r="G53" s="12"/>
       <c r="M53" s="12"/>
       <c r="S53" s="12"/>
-      <c r="Y53" s="22"/>
-    </row>
-    <row r="54" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="U53" t="s">
+        <v>361</v>
+      </c>
+      <c r="V53" t="s">
+        <v>361</v>
+      </c>
+      <c r="W53" t="s">
+        <v>361</v>
+      </c>
+      <c r="X53" t="s">
+        <v>361</v>
+      </c>
+      <c r="Y53" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="Z53" s="4" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="54" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D54" s="4" t="b">
         <v>0</v>
@@ -3520,140 +3559,137 @@
       <c r="G54" s="36"/>
       <c r="M54" s="12"/>
       <c r="S54" s="12"/>
-      <c r="Y54" s="22" t="s">
-        <v>327</v>
-      </c>
-      <c r="Z54" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="55" spans="1:26" s="4" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Y54" s="22"/>
+    </row>
+    <row r="55" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D55" s="4" t="b">
         <v>0</v>
       </c>
       <c r="E55" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F55" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="G55" s="12"/>
-      <c r="H55" s="17"/>
+        <v>1</v>
+      </c>
+      <c r="F55" s="27"/>
+      <c r="G55" s="36"/>
       <c r="M55" s="12"/>
-      <c r="N55" s="1"/>
-      <c r="O55" s="1"/>
-      <c r="R55" s="1"/>
       <c r="S55" s="12"/>
-      <c r="U55" s="1"/>
-      <c r="X55" s="1"/>
-      <c r="Y55" s="21" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="56" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="Y55" s="22" t="s">
+        <v>331</v>
+      </c>
+      <c r="Z55" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="56" spans="1:26" s="4" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
-        <v>180</v>
+        <v>61</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>181</v>
+        <v>62</v>
       </c>
       <c r="D56" s="4" t="b">
         <v>0</v>
       </c>
       <c r="E56" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F56" s="27"/>
+        <v>0</v>
+      </c>
+      <c r="F56" s="27" t="s">
+        <v>16</v>
+      </c>
       <c r="G56" s="12"/>
+      <c r="H56" s="17"/>
       <c r="M56" s="12"/>
+      <c r="N56" s="1"/>
+      <c r="O56" s="1"/>
+      <c r="R56" s="1"/>
       <c r="S56" s="12"/>
-      <c r="Y56" s="22" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="57" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A57" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="B57" s="37" t="s">
+      <c r="U56" s="1"/>
+      <c r="X56" s="1"/>
+      <c r="Y56" s="21" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="57" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A57" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D57" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E57" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57" s="27"/>
+      <c r="G57" s="12"/>
+      <c r="M57" s="12"/>
+      <c r="S57" s="12"/>
+      <c r="Y57" s="22" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="58" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A58" s="37" t="s">
+        <v>278</v>
+      </c>
+      <c r="B58" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="C57" s="38" t="s">
-        <v>276</v>
-      </c>
-      <c r="D57" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="E57" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="F57" s="27"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="9"/>
-      <c r="I57" s="9"/>
-      <c r="J57" s="9"/>
-      <c r="K57" s="9"/>
-      <c r="L57" s="9"/>
-      <c r="M57" s="14"/>
-      <c r="N57" s="9"/>
-      <c r="O57" s="9"/>
-      <c r="P57" s="9"/>
-      <c r="Q57" s="9"/>
-      <c r="R57" s="9"/>
-      <c r="S57" s="12"/>
-      <c r="U57" s="9"/>
-      <c r="X57" s="9"/>
-      <c r="Y57" s="22" t="s">
-        <v>354</v>
-      </c>
-      <c r="Z57" s="1"/>
-    </row>
-    <row r="58" spans="1:26" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A58" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" s="38" t="s">
         <v>279</v>
       </c>
-      <c r="D58" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E58" s="4" t="b">
+      <c r="D58" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="E58" s="37" t="b">
         <v>1</v>
       </c>
       <c r="F58" s="27"/>
-      <c r="G58" s="12"/>
-      <c r="M58" s="12"/>
+      <c r="G58" s="14"/>
+      <c r="H58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9"/>
+      <c r="K58" s="9"/>
+      <c r="L58" s="9"/>
+      <c r="M58" s="14"/>
+      <c r="N58" s="9"/>
+      <c r="O58" s="9"/>
+      <c r="P58" s="9"/>
+      <c r="Q58" s="9"/>
+      <c r="R58" s="9"/>
       <c r="S58" s="12"/>
+      <c r="U58" s="9"/>
+      <c r="X58" s="9"/>
       <c r="Y58" s="22" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="Z58" s="1"/>
     </row>
     <row r="59" spans="1:26" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>182</v>
+        <v>280</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>154</v>
+        <v>281</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>183</v>
+        <v>282</v>
       </c>
       <c r="D59" s="4" t="b">
         <v>0</v>
@@ -3665,18 +3701,20 @@
       <c r="G59" s="12"/>
       <c r="M59" s="12"/>
       <c r="S59" s="12"/>
-      <c r="Y59" s="22"/>
+      <c r="Y59" s="22" t="s">
+        <v>358</v>
+      </c>
       <c r="Z59" s="1"/>
     </row>
     <row r="60" spans="1:26" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
-        <v>280</v>
+        <v>185</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>86</v>
+        <v>157</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>281</v>
+        <v>186</v>
       </c>
       <c r="D60" s="4" t="b">
         <v>0</v>
@@ -3686,124 +3724,123 @@
       </c>
       <c r="F60" s="27"/>
       <c r="G60" s="12"/>
-      <c r="H60" s="16"/>
-      <c r="I60" s="16"/>
-      <c r="J60" s="16"/>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
       <c r="M60" s="12"/>
-      <c r="N60" s="16"/>
-      <c r="O60" s="16"/>
-      <c r="P60" s="16"/>
-      <c r="Q60" s="16"/>
-      <c r="R60" s="16"/>
       <c r="S60" s="12"/>
-      <c r="Y60" s="22" t="s">
-        <v>354</v>
-      </c>
+      <c r="Y60" s="22"/>
       <c r="Z60" s="1"/>
     </row>
-    <row r="61" spans="1:26" ht="29" x14ac:dyDescent="0.35">
-      <c r="A61" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="B61" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="D61" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="E61" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="F61" s="30" t="s">
+    <row r="61" spans="1:26" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A61" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="D61" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E61" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F61" s="27"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="16"/>
+      <c r="I61" s="16"/>
+      <c r="J61" s="16"/>
+      <c r="K61" s="16"/>
+      <c r="L61" s="16"/>
+      <c r="M61" s="12"/>
+      <c r="N61" s="16"/>
+      <c r="O61" s="16"/>
+      <c r="P61" s="16"/>
+      <c r="Q61" s="16"/>
+      <c r="R61" s="16"/>
+      <c r="S61" s="12"/>
+      <c r="Y61" s="22" t="s">
+        <v>358</v>
+      </c>
+      <c r="Z61" s="1"/>
+    </row>
+    <row r="62" spans="1:26" ht="29" x14ac:dyDescent="0.35">
+      <c r="A62" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="G61" s="14"/>
-      <c r="H61" s="9"/>
-      <c r="I61" s="9"/>
-      <c r="J61" s="9"/>
-      <c r="K61" s="9"/>
-      <c r="L61" s="9"/>
-      <c r="M61" s="14"/>
-      <c r="N61" s="9"/>
-      <c r="O61" s="9"/>
-      <c r="P61" s="9"/>
-      <c r="Q61" s="9"/>
-      <c r="R61" s="9"/>
-      <c r="S61" s="12"/>
-      <c r="T61" s="9"/>
-      <c r="U61" s="9"/>
-      <c r="V61" s="9"/>
-      <c r="W61" s="9"/>
-      <c r="X61" s="9"/>
-      <c r="Y61" s="22" t="s">
-        <v>354</v>
-      </c>
-      <c r="Z61" s="1"/>
-    </row>
-    <row r="62" spans="1:26" s="4" customFormat="1" ht="87" x14ac:dyDescent="0.35">
-      <c r="A62" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="D62" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E62" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F62" s="27" t="s">
+      <c r="B62" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D62" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E62" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F62" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="G62" s="14"/>
+      <c r="H62" s="9"/>
+      <c r="I62" s="9"/>
+      <c r="J62" s="9"/>
+      <c r="K62" s="9"/>
+      <c r="L62" s="9"/>
+      <c r="M62" s="14"/>
+      <c r="N62" s="9"/>
+      <c r="O62" s="9"/>
+      <c r="P62" s="9"/>
+      <c r="Q62" s="9"/>
+      <c r="R62" s="9"/>
+      <c r="S62" s="12"/>
+      <c r="T62" s="9"/>
+      <c r="U62" s="9"/>
+      <c r="V62" s="9"/>
+      <c r="W62" s="9"/>
+      <c r="X62" s="9"/>
+      <c r="Y62" s="22" t="s">
+        <v>358</v>
+      </c>
+      <c r="Z62" s="1"/>
+    </row>
+    <row r="63" spans="1:26" s="4" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+      <c r="A63" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D63" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E63" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F63" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G62" s="12"/>
-      <c r="M62" s="12"/>
-      <c r="S62" s="12"/>
-      <c r="Y62" s="22" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="63" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D63" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E63" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F63" s="27"/>
       <c r="G63" s="12"/>
       <c r="M63" s="12"/>
       <c r="S63" s="12"/>
       <c r="Y63" s="22" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="64" spans="1:26" s="1" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="64" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>291</v>
+        <v>63</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>292</v>
+        <v>64</v>
       </c>
       <c r="D64" s="4" t="b">
         <v>0</v>
@@ -3811,120 +3848,121 @@
       <c r="E64" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="F64" s="27" t="s">
-        <v>16</v>
-      </c>
+      <c r="F64" s="27"/>
       <c r="G64" s="12"/>
       <c r="M64" s="12"/>
       <c r="S64" s="12"/>
       <c r="Y64" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="Z64" s="33"/>
-    </row>
-    <row r="65" spans="1:26" s="4" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="65" spans="1:26" s="1" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>62</v>
+        <v>295</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>64</v>
+        <v>296</v>
       </c>
       <c r="D65" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E65" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" s="27" t="s">
-        <v>209</v>
+        <v>16</v>
       </c>
       <c r="G65" s="12"/>
       <c r="M65" s="12"/>
       <c r="S65" s="12"/>
       <c r="Y65" s="22" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="66" spans="1:26" s="4" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+      <c r="Z65" s="33"/>
+    </row>
+    <row r="66" spans="1:26" s="4" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>293</v>
+        <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>290</v>
+        <v>66</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>294</v>
+        <v>67</v>
       </c>
       <c r="D66" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F66" s="27"/>
+        <v>1</v>
+      </c>
+      <c r="E66" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F66" s="27" t="s">
+        <v>212</v>
+      </c>
       <c r="G66" s="12"/>
       <c r="M66" s="12"/>
       <c r="S66" s="12"/>
       <c r="Y66" s="22" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="67" spans="1:26" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A67" s="37" t="s">
-        <v>249</v>
-      </c>
-      <c r="B67" s="37" t="s">
-        <v>78</v>
-      </c>
-      <c r="C67" s="37" t="s">
-        <v>250</v>
-      </c>
-      <c r="D67" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="E67" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="F67" s="35"/>
+        <v>359</v>
+      </c>
+    </row>
+    <row r="67" spans="1:26" s="4" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A67" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="D67" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F67" s="27"/>
       <c r="G67" s="12"/>
       <c r="M67" s="12"/>
       <c r="S67" s="12"/>
       <c r="Y67" s="22" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="68" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A68" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D68" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E68" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F68" s="26" t="s">
-        <v>202</v>
-      </c>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="68" spans="1:26" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A68" s="37" t="s">
+        <v>252</v>
+      </c>
+      <c r="B68" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="C68" s="37" t="s">
+        <v>253</v>
+      </c>
+      <c r="D68" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="E68" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="F68" s="35"/>
       <c r="G68" s="12"/>
       <c r="M68" s="12"/>
       <c r="S68" s="12"/>
-    </row>
-    <row r="69" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="Y68" s="22" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="69" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="D69" s="1" t="b">
         <v>0</v>
@@ -3932,51 +3970,45 @@
       <c r="E69" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="F69" s="1" t="s">
-        <v>295</v>
+      <c r="F69" s="26" t="s">
+        <v>205</v>
       </c>
       <c r="G69" s="12"/>
       <c r="M69" s="12"/>
       <c r="S69" s="12"/>
     </row>
-    <row r="70" spans="1:26" s="1" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="B70" s="41" t="s">
-        <v>403</v>
+        <v>70</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>243</v>
+        <v>71</v>
       </c>
       <c r="D70" s="1" t="b">
         <v>0</v>
       </c>
       <c r="E70" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F70" s="26" t="s">
-        <v>242</v>
+        <v>0</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>299</v>
       </c>
       <c r="G70" s="12"/>
       <c r="M70" s="12"/>
       <c r="S70" s="12"/>
-      <c r="Y70" s="22" t="s">
-        <v>336</v>
-      </c>
-      <c r="Z70" s="1" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="71" spans="1:26" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="71" spans="1:26" s="1" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>187</v>
+        <v>244</v>
+      </c>
+      <c r="B71" s="41" t="s">
+        <v>408</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>188</v>
+        <v>246</v>
       </c>
       <c r="D71" s="1" t="b">
         <v>0</v>
@@ -3985,113 +4017,76 @@
         <v>1</v>
       </c>
       <c r="F71" s="26" t="s">
-        <v>201</v>
+        <v>245</v>
       </c>
       <c r="G71" s="12"/>
       <c r="M71" s="12"/>
       <c r="S71" s="12"/>
       <c r="Y71" s="22" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="72" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
+        <v>340</v>
+      </c>
+      <c r="Z71" s="1" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="72" spans="1:26" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
-        <v>69</v>
+        <v>189</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>10</v>
+        <v>190</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>70</v>
+        <v>191</v>
       </c>
       <c r="D72" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" s="26" t="s">
-        <v>399</v>
+        <v>204</v>
       </c>
       <c r="G72" s="12"/>
       <c r="M72" s="12"/>
       <c r="S72" s="12"/>
-    </row>
-    <row r="73" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="Y72" s="22" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="73" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
-        <v>423</v>
+        <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>424</v>
+        <v>73</v>
       </c>
       <c r="D73" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E73" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F73" s="26"/>
+        <v>0</v>
+      </c>
+      <c r="F73" s="26" t="s">
+        <v>404</v>
+      </c>
       <c r="G73" s="12"/>
-      <c r="H73" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="I73" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="J73" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="K73" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="L73" s="1" t="s">
-        <v>425</v>
-      </c>
       <c r="M73" s="12"/>
-      <c r="N73" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="O73" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="P73" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="Q73" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="R73" s="1" t="s">
-        <v>434</v>
-      </c>
       <c r="S73" s="12"/>
-      <c r="T73" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="U73" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="V73" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="W73" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="X73" s="1" t="s">
-        <v>434</v>
-      </c>
     </row>
     <row r="74" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>231</v>
+        <v>10</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D74" s="1" t="b">
         <v>0</v>
@@ -4102,62 +4097,62 @@
       <c r="F74" s="26"/>
       <c r="G74" s="12"/>
       <c r="H74" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="M74" s="12"/>
       <c r="N74" s="1" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="P74" s="1" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="Q74" s="1" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="R74" s="1" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="S74" s="12"/>
       <c r="T74" s="1" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="U74" s="1" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="V74" s="1" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="W74" s="1" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="X74" s="1" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
     <row r="75" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>10</v>
+        <v>234</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="D75" s="1" t="b">
         <v>0</v>
@@ -4168,62 +4163,62 @@
       <c r="F75" s="26"/>
       <c r="G75" s="12"/>
       <c r="H75" s="1" t="s">
-        <v>266</v>
+        <v>437</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>266</v>
+        <v>437</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>266</v>
+        <v>437</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>266</v>
+        <v>437</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>266</v>
+        <v>437</v>
       </c>
       <c r="M75" s="12"/>
       <c r="N75" s="1" t="s">
-        <v>267</v>
+        <v>438</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>267</v>
+        <v>438</v>
       </c>
       <c r="P75" s="1" t="s">
-        <v>267</v>
+        <v>438</v>
       </c>
       <c r="Q75" s="1" t="s">
-        <v>267</v>
+        <v>438</v>
       </c>
       <c r="R75" s="1" t="s">
-        <v>267</v>
+        <v>438</v>
       </c>
       <c r="S75" s="12"/>
       <c r="T75" s="1" t="s">
-        <v>268</v>
+        <v>438</v>
       </c>
       <c r="U75" s="1" t="s">
-        <v>268</v>
+        <v>438</v>
       </c>
       <c r="V75" s="1" t="s">
-        <v>268</v>
+        <v>438</v>
       </c>
       <c r="W75" s="1" t="s">
-        <v>268</v>
+        <v>438</v>
       </c>
       <c r="X75" s="1" t="s">
-        <v>268</v>
+        <v>438</v>
       </c>
     </row>
     <row r="76" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>231</v>
+        <v>10</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="D76" s="1" t="b">
         <v>0</v>
@@ -4233,19 +4228,63 @@
       </c>
       <c r="F76" s="26"/>
       <c r="G76" s="12"/>
+      <c r="H76" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>269</v>
+      </c>
       <c r="M76" s="12"/>
+      <c r="N76" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="O76" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="P76" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q76" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="R76" s="1" t="s">
+        <v>270</v>
+      </c>
       <c r="S76" s="12"/>
-      <c r="T76"/>
+      <c r="T76" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="U76" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="V76" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="W76" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="X76" s="1" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="77" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
-        <v>189</v>
+        <v>435</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>10</v>
+        <v>234</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>283</v>
+        <v>436</v>
       </c>
       <c r="D77" s="1" t="b">
         <v>0</v>
@@ -4257,60 +4296,47 @@
       <c r="G77" s="12"/>
       <c r="M77" s="12"/>
       <c r="S77" s="12"/>
-    </row>
-    <row r="78" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="B78" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C78" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="D78" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E78" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="F78" s="28" t="s">
-        <v>4</v>
-      </c>
+      <c r="T77"/>
+    </row>
+    <row r="78" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A78" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D78" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="E78" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F78" s="26"/>
       <c r="G78" s="12"/>
-      <c r="H78" s="17"/>
       <c r="M78" s="12"/>
-      <c r="N78" s="17"/>
-      <c r="O78" s="17"/>
-      <c r="R78" s="17"/>
       <c r="S78" s="12"/>
-      <c r="U78" s="17"/>
-      <c r="X78" s="17"/>
-      <c r="Y78" s="21" t="s">
-        <v>337</v>
-      </c>
-      <c r="Z78" s="12" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="79" spans="1:26" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="79" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A79" s="17" t="s">
-        <v>413</v>
+        <v>74</v>
       </c>
       <c r="B79" s="17" t="s">
         <v>5</v>
       </c>
       <c r="C79" s="17" t="s">
-        <v>414</v>
-      </c>
-      <c r="D79" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E79" s="1" t="b">
-        <v>1</v>
+        <v>75</v>
+      </c>
+      <c r="D79" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E79" s="17" t="b">
+        <v>0</v>
       </c>
       <c r="F79" s="28" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G79" s="12"/>
       <c r="H79" s="17"/>
@@ -4321,249 +4347,261 @@
       <c r="S79" s="12"/>
       <c r="U79" s="17"/>
       <c r="X79" s="17"/>
-      <c r="Y79" s="21"/>
-      <c r="Z79" s="12"/>
-    </row>
-    <row r="80" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A80" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="B80" s="1" t="s">
+      <c r="Y79" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z79" s="12" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="80" spans="1:26" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A80" s="17" t="s">
+        <v>418</v>
+      </c>
+      <c r="B80" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C80" s="1" t="s">
-        <v>220</v>
+      <c r="C80" s="17" t="s">
+        <v>419</v>
       </c>
       <c r="D80" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E80" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F80" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F80" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G80" s="12"/>
+      <c r="H80" s="17"/>
       <c r="M80" s="12"/>
+      <c r="N80" s="17"/>
+      <c r="O80" s="17"/>
+      <c r="R80" s="17"/>
       <c r="S80" s="12"/>
+      <c r="U80" s="17"/>
+      <c r="X80" s="17"/>
+      <c r="Y80" s="21"/>
+      <c r="Z80" s="12"/>
     </row>
     <row r="81" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
-        <v>73</v>
+        <v>211</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>74</v>
+        <v>223</v>
       </c>
       <c r="D81" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F81" s="26" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G81" s="12"/>
-      <c r="H81" s="17"/>
       <c r="M81" s="12"/>
-      <c r="N81" s="17"/>
-      <c r="O81" s="17"/>
-      <c r="R81" s="17"/>
       <c r="S81" s="12"/>
-      <c r="U81" s="17"/>
-      <c r="X81" s="17"/>
-    </row>
-    <row r="82" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="82" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B82" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D82" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="E82" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F82" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="G82" s="12"/>
+      <c r="H82" s="17"/>
+      <c r="M82" s="12"/>
+      <c r="N82" s="17"/>
+      <c r="O82" s="17"/>
+      <c r="R82" s="17"/>
+      <c r="S82" s="12"/>
+      <c r="U82" s="17"/>
+      <c r="X82" s="17"/>
+    </row>
+    <row r="83" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D82" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E82" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F82" s="26" t="s">
-        <v>399</v>
-      </c>
-      <c r="G82" s="12"/>
-      <c r="M82" s="12"/>
-      <c r="S82" s="12"/>
-      <c r="X82" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="83" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A83" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D83" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E83" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>256</v>
+        <v>404</v>
       </c>
       <c r="G83" s="12"/>
       <c r="M83" s="12"/>
       <c r="S83" s="12"/>
-    </row>
-    <row r="84" spans="1:26" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="X83" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="84" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
-        <v>435</v>
+        <v>80</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>436</v>
+        <v>82</v>
       </c>
       <c r="D84" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E84" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>4</v>
+        <v>259</v>
       </c>
       <c r="G84" s="12"/>
       <c r="M84" s="12"/>
       <c r="S84" s="12"/>
     </row>
-    <row r="85" spans="1:26" s="4" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A85" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B85" s="4" t="s">
+    <row r="85" spans="1:26" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A85" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D85" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E85" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F85" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="G85" s="12"/>
+      <c r="M85" s="12"/>
+      <c r="S85" s="12"/>
+    </row>
+    <row r="86" spans="1:26" s="4" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A86" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B86" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C85" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D85" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E85" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F85" s="27" t="s">
-        <v>296</v>
-      </c>
-      <c r="G85" s="12"/>
-      <c r="H85" s="17"/>
-      <c r="M85" s="12"/>
-      <c r="N85" s="17"/>
-      <c r="O85" s="17"/>
-      <c r="R85" s="17"/>
-      <c r="S85" s="12"/>
-      <c r="U85" s="17"/>
-      <c r="X85" s="17"/>
-      <c r="Y85" s="21" t="s">
-        <v>393</v>
-      </c>
-      <c r="Z85" s="4" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="86" spans="1:26" s="4" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A86" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>86</v>
-      </c>
       <c r="C86" s="4" t="s">
-        <v>298</v>
+        <v>84</v>
       </c>
       <c r="D86" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F86" s="27"/>
+        <v>1</v>
+      </c>
+      <c r="E86" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F86" s="27" t="s">
+        <v>300</v>
+      </c>
       <c r="G86" s="12"/>
       <c r="H86" s="17"/>
       <c r="M86" s="12"/>
+      <c r="N86" s="17"/>
+      <c r="O86" s="17"/>
+      <c r="R86" s="17"/>
       <c r="S86" s="12"/>
-      <c r="Y86" s="22" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="87" spans="1:26" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A87" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="D87" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E87" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F87" s="26" t="s">
-        <v>19</v>
-      </c>
+      <c r="U86" s="17"/>
+      <c r="X86" s="17"/>
+      <c r="Y86" s="21" t="s">
+        <v>398</v>
+      </c>
+      <c r="Z86" s="4" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="87" spans="1:26" s="4" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A87" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="D87" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F87" s="27"/>
       <c r="G87" s="12"/>
+      <c r="H87" s="17"/>
       <c r="M87" s="12"/>
       <c r="S87" s="12"/>
       <c r="Y87" s="22" t="s">
-        <v>338</v>
-      </c>
-      <c r="Z87" s="4"/>
-    </row>
-    <row r="88" spans="1:26" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A88" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="D88" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E88" s="4"/>
-      <c r="F88" s="27"/>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="88" spans="1:26" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A88" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D88" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="E88" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F88" s="26" t="s">
+        <v>19</v>
+      </c>
       <c r="G88" s="12"/>
       <c r="M88" s="12"/>
       <c r="S88" s="12"/>
       <c r="Y88" s="22" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="Z88" s="4"/>
     </row>
-    <row r="89" spans="1:26" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:26" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D89" s="4" t="b">
         <v>0</v>
@@ -4574,19 +4612,19 @@
       <c r="M89" s="12"/>
       <c r="S89" s="12"/>
       <c r="Y89" s="22" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="Z89" s="4"/>
     </row>
-    <row r="90" spans="1:26" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:26" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D90" s="4" t="b">
         <v>0</v>
@@ -4597,19 +4635,19 @@
       <c r="M90" s="12"/>
       <c r="S90" s="12"/>
       <c r="Y90" s="22" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="Z90" s="4"/>
     </row>
-    <row r="91" spans="1:26" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:26" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D91" s="4" t="b">
         <v>0</v>
@@ -4620,294 +4658,288 @@
       <c r="M91" s="12"/>
       <c r="S91" s="12"/>
       <c r="Y91" s="22" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="Z91" s="4"/>
     </row>
-    <row r="92" spans="1:26" s="4" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:26" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>193</v>
+        <v>312</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>173</v>
+        <v>313</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>194</v>
+        <v>311</v>
       </c>
       <c r="D92" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="E92" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F92" s="27" t="s">
-        <v>203</v>
-      </c>
+      <c r="E92" s="4"/>
+      <c r="F92" s="27"/>
       <c r="G92" s="12"/>
       <c r="M92" s="12"/>
       <c r="S92" s="12"/>
       <c r="Y92" s="22" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="93" spans="1:26" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A93" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D93" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E93" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F93" s="26" t="s">
-        <v>399</v>
+        <v>336</v>
+      </c>
+      <c r="Z92" s="4"/>
+    </row>
+    <row r="93" spans="1:26" s="4" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A93" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D93" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E93" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F93" s="27" t="s">
+        <v>206</v>
       </c>
       <c r="G93" s="12"/>
-      <c r="H93" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="J93" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="K93" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="L93" s="1" t="s">
-        <v>266</v>
-      </c>
       <c r="M93" s="12"/>
-      <c r="N93" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="O93" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="P93" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q93" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="R93" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="S93" s="12"/>
-      <c r="T93" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="U93" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="V93" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="W93" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="X93" s="1" t="s">
-        <v>268</v>
-      </c>
       <c r="Y93" s="22" t="s">
-        <v>394</v>
-      </c>
-      <c r="Z93" s="1" t="s">
-        <v>378</v>
+        <v>343</v>
       </c>
     </row>
     <row r="94" spans="1:26" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B94" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C94" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="D94" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E94" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F94" s="26" t="s">
+        <v>404</v>
+      </c>
+      <c r="G94" s="12"/>
+      <c r="H94" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="M94" s="12"/>
+      <c r="N94" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="O94" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="P94" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q94" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="R94" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="S94" s="12"/>
+      <c r="T94" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="U94" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="V94" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="W94" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="X94" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="Y94" s="22" t="s">
+        <v>399</v>
+      </c>
+      <c r="Z94" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="95" spans="1:26" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A95" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D94" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E94" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F94" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="G94" s="12"/>
-      <c r="M94" s="12"/>
-      <c r="S94" s="12"/>
-      <c r="Y94" s="22" t="s">
-        <v>340</v>
-      </c>
-      <c r="Z94" s="1" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="95" spans="1:26" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A95" s="4" t="s">
+      <c r="B95" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D95" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E95" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F95" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="B95" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C95" s="4" t="s">
+      <c r="G95" s="12"/>
+      <c r="M95" s="12"/>
+      <c r="S95" s="12"/>
+      <c r="Y95" s="22" t="s">
+        <v>344</v>
+      </c>
+      <c r="Z95" s="1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="96" spans="1:26" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A96" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D95" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E95" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F95" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="G95" s="12"/>
-      <c r="H95" s="1"/>
-      <c r="M95" s="12"/>
-      <c r="N95" s="1"/>
-      <c r="O95" s="1"/>
-      <c r="R95" s="1"/>
-      <c r="S95" s="12"/>
-      <c r="U95" s="1"/>
-      <c r="X95" s="1"/>
-      <c r="Y95" s="21" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="96" spans="1:26" s="4" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="4" t="s">
-        <v>144</v>
-      </c>
       <c r="B96" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D96" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E96" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F96" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="G96" s="12"/>
+      <c r="H96" s="1"/>
+      <c r="M96" s="12"/>
+      <c r="N96" s="1"/>
+      <c r="O96" s="1"/>
+      <c r="R96" s="1"/>
+      <c r="S96" s="12"/>
+      <c r="U96" s="1"/>
+      <c r="X96" s="1"/>
+      <c r="Y96" s="21" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="97" spans="1:26" s="4" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B97" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C96" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="D96" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E96" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F96" s="27" t="s">
+      <c r="C97" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D97" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E97" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F97" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="G96" s="12"/>
-      <c r="M96" s="12"/>
-      <c r="S96" s="12"/>
-      <c r="Y96" s="22" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="97" spans="1:26" s="4" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="17" t="s">
-        <v>418</v>
-      </c>
-      <c r="B97" s="17" t="s">
+      <c r="G97" s="12"/>
+      <c r="M97" s="12"/>
+      <c r="S97" s="12"/>
+      <c r="Y97" s="22" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="98" spans="1:26" s="4" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="17" t="s">
+        <v>423</v>
+      </c>
+      <c r="B98" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C97" s="17" t="s">
-        <v>419</v>
-      </c>
-      <c r="D97" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="E97" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F97" s="17" t="s">
+      <c r="C98" s="17" t="s">
+        <v>424</v>
+      </c>
+      <c r="D98" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E98" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F98" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G97" s="12"/>
-      <c r="L97" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="M97" s="12"/>
-      <c r="R97" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="S97" s="12"/>
-      <c r="X97" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y97" s="22"/>
-    </row>
-    <row r="98" spans="1:26" s="1" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A98" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D98" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E98" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F98" s="26" t="s">
-        <v>93</v>
-      </c>
       <c r="G98" s="12"/>
+      <c r="L98" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="M98" s="12"/>
+      <c r="R98" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="S98" s="12"/>
-    </row>
-    <row r="99" spans="1:26" s="1" customFormat="1" ht="116" x14ac:dyDescent="0.35">
-      <c r="A99" s="32" t="s">
-        <v>310</v>
-      </c>
-      <c r="B99" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="C99" s="32" t="s">
-        <v>311</v>
-      </c>
-      <c r="D99" s="32" t="b">
+      <c r="X98" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y98" s="22"/>
+    </row>
+    <row r="99" spans="1:26" s="1" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A99" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D99" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E99" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F99" s="26" t="s">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="G99" s="12"/>
       <c r="M99" s="12"/>
       <c r="S99" s="12"/>
-      <c r="Y99" s="22" t="s">
-        <v>395</v>
-      </c>
-      <c r="Z99" s="1" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="100" spans="1:26" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="100" spans="1:26" s="1" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A100" s="32" t="s">
-        <v>215</v>
+        <v>314</v>
       </c>
       <c r="B100" s="32" t="s">
         <v>5</v>
       </c>
       <c r="C100" s="32" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D100" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="E100" s="32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F100" s="26" t="s">
         <v>4</v>
@@ -4915,24 +4947,27 @@
       <c r="G100" s="12"/>
       <c r="M100" s="12"/>
       <c r="S100" s="12"/>
-      <c r="Z100" s="12" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="101" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A101" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B101" s="1" t="s">
+      <c r="Y100" s="22" t="s">
+        <v>400</v>
+      </c>
+      <c r="Z100" s="1" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="101" spans="1:26" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A101" s="32" t="s">
+        <v>218</v>
+      </c>
+      <c r="B101" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D101" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E101" s="1" t="b">
+      <c r="C101" s="32" t="s">
+        <v>316</v>
+      </c>
+      <c r="D101" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="E101" s="32" t="b">
         <v>1</v>
       </c>
       <c r="F101" s="26" t="s">
@@ -4941,77 +4976,77 @@
       <c r="G101" s="12"/>
       <c r="M101" s="12"/>
       <c r="S101" s="12"/>
-      <c r="Y101" s="22" t="s">
-        <v>327</v>
-      </c>
-      <c r="Z101" s="1" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="102" spans="1:26" s="1" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="Z101" s="12" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="102" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>96</v>
+        <v>150</v>
       </c>
       <c r="D102" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E102" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102" s="26" t="s">
-        <v>255</v>
+        <v>4</v>
       </c>
       <c r="G102" s="12"/>
       <c r="M102" s="12"/>
       <c r="S102" s="12"/>
       <c r="Y102" s="22" t="s">
-        <v>396</v>
+        <v>331</v>
       </c>
       <c r="Z102" s="1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="103" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A103" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B103" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="C103" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="D103" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E103" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F103" s="27" t="s">
-        <v>400</v>
+        <v>386</v>
+      </c>
+    </row>
+    <row r="103" spans="1:26" s="1" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A103" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D103" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E103" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F103" s="26" t="s">
+        <v>258</v>
       </c>
       <c r="G103" s="12"/>
       <c r="M103" s="12"/>
       <c r="S103" s="12"/>
       <c r="Y103" s="22" t="s">
-        <v>327</v>
+        <v>401</v>
+      </c>
+      <c r="Z103" s="1" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="104" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>237</v>
+        <v>198</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>239</v>
+        <v>200</v>
       </c>
       <c r="D104" s="4" t="b">
         <v>0</v>
@@ -5019,177 +5054,180 @@
       <c r="E104" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="F104" s="39"/>
+      <c r="F104" s="27" t="s">
+        <v>405</v>
+      </c>
       <c r="G104" s="12"/>
       <c r="M104" s="12"/>
       <c r="S104" s="12"/>
       <c r="Y104" s="22" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="105" spans="1:26" s="1" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="105" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>211</v>
+        <v>240</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>10</v>
+        <v>241</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>313</v>
+        <v>242</v>
       </c>
       <c r="D105" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="F105" s="27" t="s">
-        <v>209</v>
-      </c>
+      <c r="F105" s="39"/>
       <c r="G105" s="12"/>
       <c r="M105" s="12"/>
       <c r="S105" s="12"/>
       <c r="Y105" s="22" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="106" spans="1:26" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D106" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E106" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F106" s="26" t="s">
-        <v>16</v>
+        <v>331</v>
+      </c>
+    </row>
+    <row r="106" spans="1:26" s="1" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A106" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="D106" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E106" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F106" s="27" t="s">
+        <v>212</v>
       </c>
       <c r="G106" s="12"/>
       <c r="M106" s="12"/>
       <c r="S106" s="12"/>
-    </row>
-    <row r="107" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="B107" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="D107" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E107" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F107" s="35" t="s">
-        <v>209</v>
+      <c r="Y106" s="22" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="107" spans="1:26" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A107" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D107" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="E107" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F107" s="26" t="s">
+        <v>16</v>
       </c>
       <c r="G107" s="12"/>
-      <c r="H107" s="1"/>
       <c r="M107" s="12"/>
       <c r="S107" s="12"/>
     </row>
-    <row r="108" spans="1:26" s="1" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D108" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E108" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F108" s="29" t="s">
-        <v>401</v>
+    <row r="108" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A108" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="D108" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E108" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F108" s="35" t="s">
+        <v>212</v>
       </c>
       <c r="G108" s="12"/>
+      <c r="H108" s="1"/>
       <c r="M108" s="12"/>
       <c r="S108" s="12"/>
-      <c r="Y108" s="22" t="s">
-        <v>397</v>
-      </c>
-      <c r="Z108" s="12" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="109" spans="1:26" s="1" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A109" s="33" t="s">
-        <v>314</v>
-      </c>
-      <c r="B109" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C109" s="22" t="s">
-        <v>315</v>
-      </c>
-      <c r="D109" s="22" t="b">
-        <v>0</v>
-      </c>
-      <c r="E109" s="22" t="b">
+    </row>
+    <row r="109" spans="1:26" s="1" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A109" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D109" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="E109" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F109" s="29" t="s">
-        <v>16</v>
+        <v>406</v>
       </c>
       <c r="G109" s="12"/>
       <c r="M109" s="12"/>
       <c r="S109" s="12"/>
       <c r="Y109" s="22" t="s">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="Z109" s="12" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="110" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A110" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B110" s="1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="110" spans="1:26" s="1" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A110" s="33" t="s">
+        <v>318</v>
+      </c>
+      <c r="B110" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C110" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D110" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E110" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F110" s="26" t="s">
-        <v>4</v>
+      <c r="C110" s="22" t="s">
+        <v>319</v>
+      </c>
+      <c r="D110" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="E110" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="F110" s="29" t="s">
+        <v>16</v>
       </c>
       <c r="G110" s="12"/>
       <c r="M110" s="12"/>
       <c r="S110" s="12"/>
-    </row>
-    <row r="111" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="Y110" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="Z110" s="12" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="111" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
-        <v>198</v>
+        <v>104</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>199</v>
+        <v>105</v>
       </c>
       <c r="D111" s="1" t="b">
         <v>0</v>
@@ -5198,7 +5236,7 @@
         <v>1</v>
       </c>
       <c r="F111" s="26" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G111" s="12"/>
       <c r="M111" s="12"/>
@@ -5206,94 +5244,82 @@
     </row>
     <row r="112" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
-        <v>103</v>
+        <v>201</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>105</v>
+        <v>5</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>106</v>
+        <v>202</v>
       </c>
       <c r="D112" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E112" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="26" t="s">
-        <v>104</v>
+        <v>16</v>
       </c>
       <c r="G112" s="12"/>
       <c r="M112" s="12"/>
       <c r="S112" s="12"/>
     </row>
-    <row r="113" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D113" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E113" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F113" s="26" t="s">
         <v>107</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D113" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E113" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F113" s="26" t="s">
-        <v>399</v>
       </c>
       <c r="G113" s="12"/>
       <c r="M113" s="12"/>
       <c r="S113" s="12"/>
     </row>
-    <row r="114" spans="1:26" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A114" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B114" s="4" t="s">
+    <row r="114" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A114" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D114" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E114" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F114" s="26" t="s">
+        <v>404</v>
+      </c>
+      <c r="G114" s="12"/>
+      <c r="M114" s="12"/>
+      <c r="S114" s="12"/>
+    </row>
+    <row r="115" spans="1:26" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A115" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B115" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C114" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D114" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E114" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F114" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="G114" s="12"/>
-      <c r="H114" s="1"/>
-      <c r="M114" s="12"/>
-      <c r="N114" s="1"/>
-      <c r="O114" s="1"/>
-      <c r="R114" s="1"/>
-      <c r="S114" s="12"/>
-      <c r="U114" s="1"/>
-      <c r="X114" s="1"/>
-      <c r="Y114" s="21" t="s">
-        <v>341</v>
-      </c>
-      <c r="Z114" s="4" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="115" spans="1:26" s="4" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A115" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B115" s="4" t="s">
-        <v>63</v>
-      </c>
       <c r="C115" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D115" s="4" t="b">
         <v>1</v>
@@ -5302,131 +5328,107 @@
         <v>0</v>
       </c>
       <c r="F115" s="27" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G115" s="12"/>
       <c r="H115" s="1"/>
       <c r="M115" s="12"/>
+      <c r="N115" s="1"/>
+      <c r="O115" s="1"/>
+      <c r="R115" s="1"/>
       <c r="S115" s="12"/>
+      <c r="U115" s="1"/>
+      <c r="X115" s="1"/>
       <c r="Y115" s="21" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="Z115" s="4" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="116" spans="1:26" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A116" t="s">
-        <v>113</v>
-      </c>
-      <c r="B116" t="s">
-        <v>5</v>
-      </c>
-      <c r="C116" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="116" spans="1:26" s="4" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A116" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D116" t="b">
-        <v>1</v>
-      </c>
-      <c r="E116" t="b">
-        <v>1</v>
-      </c>
-      <c r="F116" s="28" t="s">
-        <v>16</v>
+      <c r="B116" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D116" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E116" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F116" s="27" t="s">
+        <v>212</v>
       </c>
       <c r="G116" s="12"/>
       <c r="H116" s="1"/>
       <c r="M116" s="12"/>
-      <c r="N116" s="1"/>
-      <c r="O116" s="1"/>
-      <c r="R116" s="1"/>
       <c r="S116" s="12"/>
       <c r="Y116" s="21" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="Z116" s="4" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="117" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B117" s="1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="117" spans="1:26" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
         <v>5</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D117" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E117" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F117" s="34" t="s">
+      <c r="C117" t="s">
+        <v>117</v>
+      </c>
+      <c r="D117" t="b">
+        <v>1</v>
+      </c>
+      <c r="E117" t="b">
+        <v>1</v>
+      </c>
+      <c r="F117" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G117" s="12"/>
-      <c r="I117" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J117" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K117" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L117" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="H117" s="1"/>
       <c r="M117" s="12"/>
-      <c r="O117" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="P117" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q117" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="R117" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="N117" s="1"/>
+      <c r="O117" s="1"/>
+      <c r="R117" s="1"/>
       <c r="S117" s="12"/>
-      <c r="U117" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="V117" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W117" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="X117" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="118" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A118" s="32" t="s">
-        <v>117</v>
-      </c>
-      <c r="B118" s="32" t="s">
+      <c r="Y117" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="Z117" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="118" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A118" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C118" s="32" t="s">
-        <v>316</v>
-      </c>
-      <c r="D118" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="E118" s="32" t="b">
+      <c r="C118" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D118" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="E118" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F118" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G118" s="24"/>
+      <c r="G118" s="12"/>
       <c r="I118" s="1" t="s">
         <v>4</v>
       </c>
@@ -5466,18 +5468,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A119" s="32" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B119" s="32" t="s">
         <v>5</v>
       </c>
       <c r="C119" s="32" t="s">
-        <v>119</v>
+        <v>320</v>
       </c>
       <c r="D119" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E119" s="32" t="b">
         <v>1</v>
@@ -5486,6 +5488,18 @@
         <v>16</v>
       </c>
       <c r="G119" s="24"/>
+      <c r="I119" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J119" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K119" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L119" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="M119" s="12"/>
       <c r="O119" s="1" t="s">
         <v>4</v>
@@ -5513,196 +5527,184 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A120" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="B120" s="4" t="s">
+    <row r="120" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A120" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="B120" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="C120" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="D120" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E120" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F120" s="27"/>
+      <c r="C120" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="D120" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E120" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="F120" s="34" t="s">
+        <v>16</v>
+      </c>
       <c r="G120" s="24"/>
-      <c r="I120"/>
-      <c r="J120"/>
-      <c r="K120"/>
-      <c r="L120"/>
       <c r="M120" s="12"/>
+      <c r="O120" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="P120" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q120" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="R120" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="S120" s="12"/>
-    </row>
-    <row r="121" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="B121" s="5" t="s">
+      <c r="U120" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="V120" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="W120" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X120" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A121" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B121" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C121" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="D121" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="E121" s="5" t="b">
+      <c r="C121" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D121" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E121" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F121" s="27"/>
       <c r="G121" s="24"/>
-      <c r="H121" s="1"/>
       <c r="I121"/>
       <c r="J121"/>
       <c r="K121"/>
       <c r="L121"/>
       <c r="M121" s="12"/>
-      <c r="N121"/>
-      <c r="O121"/>
-      <c r="P121"/>
-      <c r="Q121"/>
-      <c r="R121"/>
       <c r="S121" s="12"/>
-      <c r="T121"/>
-      <c r="U121"/>
-      <c r="V121"/>
-      <c r="W121"/>
-      <c r="X121"/>
-    </row>
-    <row r="122" spans="1:26" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A122" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="B122" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="C122" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="D122" s="23" t="b">
-        <v>1</v>
-      </c>
-      <c r="E122" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="F122" s="28" t="s">
-        <v>19</v>
-      </c>
+    </row>
+    <row r="122" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A122" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="D122" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E122" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F122" s="27"/>
       <c r="G122" s="24"/>
       <c r="H122" s="1"/>
-      <c r="I122" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="J122" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="K122" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="L122" s="1" t="s">
-        <v>351</v>
-      </c>
+      <c r="I122"/>
+      <c r="J122"/>
+      <c r="K122"/>
+      <c r="L122"/>
       <c r="M122" s="12"/>
-      <c r="N122" s="1"/>
-      <c r="O122" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="P122" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="Q122" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="R122" s="1" t="s">
-        <v>351</v>
-      </c>
+      <c r="N122"/>
+      <c r="O122"/>
+      <c r="P122"/>
+      <c r="Q122"/>
+      <c r="R122"/>
       <c r="S122" s="12"/>
-      <c r="U122" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="V122" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="W122" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="X122" s="1" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="123" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="32" t="s">
+      <c r="T122"/>
+      <c r="U122"/>
+      <c r="V122"/>
+      <c r="W122"/>
+      <c r="X122"/>
+    </row>
+    <row r="123" spans="1:26" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A123" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="B123" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="C123" s="32" t="s">
+      <c r="B123" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="D123" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="E123" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="F123" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="G123" s="12"/>
+      <c r="C123" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="D123" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="E123" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="F123" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G123" s="24"/>
+      <c r="H123" s="1"/>
       <c r="I123" s="1" t="s">
-        <v>4</v>
+        <v>355</v>
       </c>
       <c r="J123" s="1" t="s">
-        <v>4</v>
+        <v>355</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>4</v>
+        <v>355</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>4</v>
+        <v>355</v>
       </c>
       <c r="M123" s="12"/>
+      <c r="N123" s="1"/>
       <c r="O123" s="1" t="s">
-        <v>4</v>
+        <v>355</v>
       </c>
       <c r="P123" s="1" t="s">
-        <v>4</v>
+        <v>355</v>
       </c>
       <c r="Q123" s="1" t="s">
-        <v>4</v>
+        <v>355</v>
       </c>
       <c r="R123" s="1" t="s">
-        <v>4</v>
+        <v>355</v>
       </c>
       <c r="S123" s="12"/>
       <c r="U123" s="1" t="s">
-        <v>4</v>
+        <v>355</v>
       </c>
       <c r="V123" s="1" t="s">
-        <v>4</v>
+        <v>355</v>
       </c>
       <c r="W123" s="1" t="s">
-        <v>4</v>
+        <v>355</v>
       </c>
       <c r="X123" s="1" t="s">
-        <v>4</v>
+        <v>355</v>
       </c>
     </row>
     <row r="124" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A124" s="32" t="s">
-        <v>229</v>
+        <v>126</v>
       </c>
       <c r="B124" s="32" t="s">
         <v>5</v>
       </c>
       <c r="C124" s="32" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D124" s="32" t="b">
         <v>1</v>
@@ -5710,10 +5712,10 @@
       <c r="E124" s="32" t="b">
         <v>1</v>
       </c>
-      <c r="F124" s="34" t="s">
+      <c r="F124" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="G124" s="24"/>
+      <c r="G124" s="12"/>
       <c r="I124" s="1" t="s">
         <v>4</v>
       </c>
@@ -5755,118 +5757,165 @@
     </row>
     <row r="125" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A125" s="32" t="s">
-        <v>126</v>
+        <v>232</v>
       </c>
       <c r="B125" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="C125" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="D125" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="E125" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="F125" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="G125" s="24"/>
+      <c r="I125" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J125" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K125" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L125" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M125" s="12"/>
+      <c r="O125" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="P125" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q125" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="R125" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="S125" s="12"/>
+      <c r="U125" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="V125" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="W125" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X125" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A126" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="B126" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C125" s="32" t="s">
-        <v>127</v>
-      </c>
-      <c r="D125" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="E125" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="F125" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="G125" s="24"/>
-      <c r="M125" s="12"/>
-      <c r="S125" s="12"/>
-    </row>
-    <row r="126" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A126" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="D126" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E126" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G126" s="12"/>
+      <c r="C126" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="D126" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="E126" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="F126" s="26" t="s">
+        <v>300</v>
+      </c>
+      <c r="G126" s="24"/>
       <c r="M126" s="12"/>
       <c r="S126" s="12"/>
     </row>
-    <row r="127" spans="1:26" s="1" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A127" s="32" t="s">
-        <v>244</v>
-      </c>
-      <c r="B127" s="32" t="s">
-        <v>78</v>
-      </c>
-      <c r="C127" s="32" t="s">
-        <v>245</v>
-      </c>
-      <c r="D127" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="E127" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="F127" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="G127" s="24"/>
+    <row r="127" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A127" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D127" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E127" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G127" s="12"/>
       <c r="M127" s="12"/>
       <c r="S127" s="12"/>
-      <c r="Y127" s="22" t="s">
-        <v>343</v>
-      </c>
-      <c r="Z127" s="1" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="128" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="128" spans="1:26" s="1" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A128" s="32" t="s">
-        <v>128</v>
+        <v>247</v>
       </c>
       <c r="B128" s="32" t="s">
-        <v>129</v>
+        <v>81</v>
       </c>
       <c r="C128" s="32" t="s">
-        <v>130</v>
+        <v>248</v>
       </c>
       <c r="D128" s="32" t="b">
         <v>1</v>
       </c>
       <c r="E128" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128" s="26" t="s">
-        <v>217</v>
+        <v>249</v>
       </c>
       <c r="G128" s="24"/>
       <c r="M128" s="12"/>
       <c r="S128" s="12"/>
       <c r="Y128" s="22" t="s">
-        <v>361</v>
+        <v>347</v>
       </c>
       <c r="Z128" s="1" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A129" s="20"/>
-      <c r="B129" s="20"/>
-      <c r="C129" s="20"/>
-      <c r="D129" s="20"/>
-      <c r="E129" s="20"/>
-      <c r="F129" s="20"/>
-      <c r="G129" s="25"/>
-      <c r="H129" s="19"/>
-      <c r="N129" s="1"/>
+        <v>392</v>
+      </c>
+    </row>
+    <row r="129" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A129" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="B129" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="C129" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="D129" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="E129" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="F129" s="26" t="s">
+        <v>220</v>
+      </c>
+      <c r="G129" s="24"/>
+      <c r="M129" s="12"/>
       <c r="S129" s="12"/>
-    </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="Y129" s="22" t="s">
+        <v>365</v>
+      </c>
+      <c r="Z129" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="130" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A130" s="20"/>
       <c r="B130" s="20"/>
       <c r="C130" s="20"/>
@@ -5875,9 +5924,11 @@
       <c r="F130" s="20"/>
       <c r="G130" s="25"/>
       <c r="H130" s="19"/>
+      <c r="M130" s="15"/>
+      <c r="N130" s="1"/>
       <c r="S130" s="12"/>
     </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A131" s="20"/>
       <c r="B131" s="20"/>
       <c r="C131" s="20"/>
@@ -5886,9 +5937,10 @@
       <c r="F131" s="20"/>
       <c r="G131" s="25"/>
       <c r="H131" s="19"/>
+      <c r="M131" s="15"/>
       <c r="S131" s="12"/>
     </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A132" s="20"/>
       <c r="B132" s="20"/>
       <c r="C132" s="20"/>
@@ -5897,9 +5949,10 @@
       <c r="F132" s="20"/>
       <c r="G132" s="25"/>
       <c r="H132" s="19"/>
+      <c r="M132" s="15"/>
       <c r="S132" s="12"/>
     </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A133" s="20"/>
       <c r="B133" s="20"/>
       <c r="C133" s="20"/>
@@ -5908,9 +5961,10 @@
       <c r="F133" s="20"/>
       <c r="G133" s="25"/>
       <c r="H133" s="19"/>
+      <c r="M133" s="15"/>
       <c r="S133" s="12"/>
     </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A134" s="20"/>
       <c r="B134" s="20"/>
       <c r="C134" s="20"/>
@@ -5919,9 +5973,10 @@
       <c r="F134" s="20"/>
       <c r="G134" s="25"/>
       <c r="H134" s="19"/>
+      <c r="M134" s="15"/>
       <c r="S134" s="12"/>
     </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A135" s="20"/>
       <c r="B135" s="20"/>
       <c r="C135" s="20"/>
@@ -5930,9 +5985,10 @@
       <c r="F135" s="20"/>
       <c r="G135" s="25"/>
       <c r="H135" s="19"/>
+      <c r="M135" s="15"/>
       <c r="S135" s="12"/>
     </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A136" s="20"/>
       <c r="B136" s="20"/>
       <c r="C136" s="20"/>
@@ -5941,9 +5997,10 @@
       <c r="F136" s="20"/>
       <c r="G136" s="25"/>
       <c r="H136" s="19"/>
+      <c r="M136" s="15"/>
       <c r="S136" s="12"/>
     </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A137" s="20"/>
       <c r="B137" s="20"/>
       <c r="C137" s="20"/>
@@ -5952,9 +6009,10 @@
       <c r="F137" s="20"/>
       <c r="G137" s="25"/>
       <c r="H137" s="19"/>
+      <c r="M137" s="15"/>
       <c r="S137" s="12"/>
     </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A138" s="20"/>
       <c r="B138" s="20"/>
       <c r="C138" s="20"/>
@@ -5962,9 +6020,11 @@
       <c r="E138" s="20"/>
       <c r="F138" s="20"/>
       <c r="G138" s="25"/>
+      <c r="H138" s="19"/>
+      <c r="M138" s="15"/>
       <c r="S138" s="12"/>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A139" s="20"/>
       <c r="B139" s="20"/>
       <c r="C139" s="20"/>
@@ -5972,9 +6032,10 @@
       <c r="E139" s="20"/>
       <c r="F139" s="20"/>
       <c r="G139" s="25"/>
+      <c r="M139" s="15"/>
       <c r="S139" s="12"/>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A140" s="20"/>
       <c r="B140" s="20"/>
       <c r="C140" s="20"/>
@@ -5982,9 +6043,10 @@
       <c r="E140" s="20"/>
       <c r="F140" s="20"/>
       <c r="G140" s="25"/>
+      <c r="M140" s="15"/>
       <c r="S140" s="12"/>
     </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A141" s="20"/>
       <c r="B141" s="20"/>
       <c r="C141" s="20"/>
@@ -5992,9 +6054,10 @@
       <c r="E141" s="20"/>
       <c r="F141" s="20"/>
       <c r="G141" s="25"/>
+      <c r="M141" s="15"/>
       <c r="S141" s="12"/>
     </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A142" s="20"/>
       <c r="B142" s="20"/>
       <c r="C142" s="20"/>
@@ -6002,9 +6065,10 @@
       <c r="E142" s="20"/>
       <c r="F142" s="20"/>
       <c r="G142" s="25"/>
+      <c r="M142" s="15"/>
       <c r="S142" s="12"/>
     </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A143" s="20"/>
       <c r="B143" s="20"/>
       <c r="C143" s="20"/>
@@ -6012,9 +6076,10 @@
       <c r="E143" s="20"/>
       <c r="F143" s="20"/>
       <c r="G143" s="25"/>
+      <c r="M143" s="15"/>
       <c r="S143" s="12"/>
     </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A144" s="20"/>
       <c r="B144" s="20"/>
       <c r="C144" s="20"/>
@@ -6022,9 +6087,10 @@
       <c r="E144" s="20"/>
       <c r="F144" s="20"/>
       <c r="G144" s="25"/>
+      <c r="M144" s="15"/>
       <c r="S144" s="12"/>
     </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A145" s="20"/>
       <c r="B145" s="20"/>
       <c r="C145" s="20"/>
@@ -6032,9 +6098,10 @@
       <c r="E145" s="20"/>
       <c r="F145" s="20"/>
       <c r="G145" s="25"/>
+      <c r="M145" s="15"/>
       <c r="S145" s="12"/>
     </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A146" s="20"/>
       <c r="B146" s="20"/>
       <c r="C146" s="20"/>
@@ -6042,9 +6109,10 @@
       <c r="E146" s="20"/>
       <c r="F146" s="20"/>
       <c r="G146" s="25"/>
+      <c r="M146" s="15"/>
       <c r="S146" s="12"/>
     </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A147" s="20"/>
       <c r="B147" s="20"/>
       <c r="C147" s="20"/>
@@ -6052,9 +6120,10 @@
       <c r="E147" s="20"/>
       <c r="F147" s="20"/>
       <c r="G147" s="25"/>
+      <c r="M147" s="15"/>
       <c r="S147" s="12"/>
     </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A148" s="20"/>
       <c r="B148" s="20"/>
       <c r="C148" s="20"/>
@@ -6062,9 +6131,10 @@
       <c r="E148" s="20"/>
       <c r="F148" s="20"/>
       <c r="G148" s="25"/>
+      <c r="M148" s="15"/>
       <c r="S148" s="12"/>
     </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A149" s="20"/>
       <c r="B149" s="20"/>
       <c r="C149" s="20"/>
@@ -6072,9 +6142,10 @@
       <c r="E149" s="20"/>
       <c r="F149" s="20"/>
       <c r="G149" s="25"/>
+      <c r="M149" s="15"/>
       <c r="S149" s="12"/>
     </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A150" s="20"/>
       <c r="B150" s="20"/>
       <c r="C150" s="20"/>
@@ -6082,9 +6153,10 @@
       <c r="E150" s="20"/>
       <c r="F150" s="20"/>
       <c r="G150" s="25"/>
+      <c r="M150" s="15"/>
       <c r="S150" s="12"/>
     </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A151" s="20"/>
       <c r="B151" s="20"/>
       <c r="C151" s="20"/>
@@ -6092,9 +6164,10 @@
       <c r="E151" s="20"/>
       <c r="F151" s="20"/>
       <c r="G151" s="25"/>
+      <c r="M151" s="15"/>
       <c r="S151" s="12"/>
     </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A152" s="20"/>
       <c r="B152" s="20"/>
       <c r="C152" s="20"/>
@@ -6102,9 +6175,10 @@
       <c r="E152" s="20"/>
       <c r="F152" s="20"/>
       <c r="G152" s="25"/>
+      <c r="M152" s="15"/>
       <c r="S152" s="12"/>
     </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A153" s="20"/>
       <c r="B153" s="20"/>
       <c r="C153" s="20"/>
@@ -6112,9 +6186,10 @@
       <c r="E153" s="20"/>
       <c r="F153" s="20"/>
       <c r="G153" s="25"/>
+      <c r="M153" s="15"/>
       <c r="S153" s="12"/>
     </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A154" s="20"/>
       <c r="B154" s="20"/>
       <c r="C154" s="20"/>
@@ -6122,9 +6197,10 @@
       <c r="E154" s="20"/>
       <c r="F154" s="20"/>
       <c r="G154" s="25"/>
+      <c r="M154" s="15"/>
       <c r="S154" s="12"/>
     </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A155" s="20"/>
       <c r="B155" s="20"/>
       <c r="C155" s="20"/>
@@ -6132,9 +6208,10 @@
       <c r="E155" s="20"/>
       <c r="F155" s="20"/>
       <c r="G155" s="25"/>
+      <c r="M155" s="15"/>
       <c r="S155" s="12"/>
     </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A156" s="20"/>
       <c r="B156" s="20"/>
       <c r="C156" s="20"/>
@@ -6142,9 +6219,10 @@
       <c r="E156" s="20"/>
       <c r="F156" s="20"/>
       <c r="G156" s="25"/>
+      <c r="M156" s="15"/>
       <c r="S156" s="12"/>
     </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A157" s="20"/>
       <c r="B157" s="20"/>
       <c r="C157" s="20"/>
@@ -6152,9 +6230,10 @@
       <c r="E157" s="20"/>
       <c r="F157" s="20"/>
       <c r="G157" s="25"/>
+      <c r="M157" s="15"/>
       <c r="S157" s="12"/>
     </row>
-    <row r="158" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A158" s="20"/>
       <c r="B158" s="20"/>
       <c r="C158" s="20"/>
@@ -6162,9 +6241,10 @@
       <c r="E158" s="20"/>
       <c r="F158" s="20"/>
       <c r="G158" s="25"/>
+      <c r="M158" s="15"/>
       <c r="S158" s="12"/>
     </row>
-    <row r="159" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A159" s="20"/>
       <c r="B159" s="20"/>
       <c r="C159" s="20"/>
@@ -6172,27 +6252,41 @@
       <c r="E159" s="20"/>
       <c r="F159" s="20"/>
       <c r="G159" s="25"/>
+      <c r="M159" s="15"/>
+      <c r="S159" s="12"/>
+    </row>
+    <row r="160" spans="1:26" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A160" s="20"/>
+      <c r="B160" s="20"/>
+      <c r="C160" s="20"/>
+      <c r="D160" s="20"/>
+      <c r="E160" s="20"/>
+      <c r="F160" s="20"/>
+      <c r="G160" s="25"/>
+      <c r="M160" s="15"/>
+      <c r="S160" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="Y45:Y46"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
     <mergeCell ref="Y7:Y8"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D7:D8"/>
+    <mergeCell ref="Y46:Y47"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:D47"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="H20" r:id="rId1" display="standaarden.ondersteuning@vng.nl" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="F20" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="F45" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="37" fitToHeight="0" orientation="landscape" r:id="rId3"/>
+  <pageSetup paperSize="9" scale="37" fitToHeight="0" orientation="landscape" r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -6207,48 +6301,48 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B4" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="1:2" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B6" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B7" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B8" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
